--- a/lf_comp_plotly.xlsx
+++ b/lf_comp_plotly.xlsx
@@ -1,28 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cityofaustin-my.sharepoint.com/personal/sarah_courtney_austintexas_gov/Documents/Documents/demographics-jobs-study/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\courtneys\Documents\GitHub\demographics-jobs-study\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="125" documentId="8_{84F985C9-8522-4DCB-89C7-1CB1E7ECB0AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{580848AE-27B3-41C3-A46F-0D2F0BBB502F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8817CE21-4EEC-41A8-96DF-846E9040C16E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{2F18592C-C18A-41E0-8BC6-B3796543A0A5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="7" xr2:uid="{2F18592C-C18A-41E0-8BC6-B3796543A0A5}"/>
   </bookViews>
   <sheets>
     <sheet name="earnings" sheetId="5" r:id="rId1"/>
     <sheet name="sector" sheetId="4" r:id="rId2"/>
-    <sheet name="age" sheetId="2" r:id="rId3"/>
-    <sheet name="edu" sheetId="1" r:id="rId4"/>
-    <sheet name="race" sheetId="3" r:id="rId5"/>
-    <sheet name="industry" sheetId="7" r:id="rId6"/>
-    <sheet name="transpo" sheetId="8" r:id="rId7"/>
-    <sheet name="Notes" sheetId="6" r:id="rId8"/>
+    <sheet name="age_city" sheetId="2" r:id="rId3"/>
+    <sheet name="age_msa" sheetId="9" r:id="rId4"/>
+    <sheet name="edu_city" sheetId="1" r:id="rId5"/>
+    <sheet name="edu_msa" sheetId="10" r:id="rId6"/>
+    <sheet name="race_city" sheetId="3" r:id="rId7"/>
+    <sheet name="race_msa" sheetId="11" r:id="rId8"/>
+    <sheet name="industry" sheetId="7" r:id="rId9"/>
+    <sheet name="transpo" sheetId="8" r:id="rId10"/>
+    <sheet name="Notes" sheetId="6" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="191029" calcOnSave="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -43,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="84">
   <si>
     <t>Age</t>
   </si>
@@ -493,7 +496,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -546,6 +549,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1267,6 +1273,1141 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53D66845-253C-4802-AFB8-DEDA69A5A8E7}">
+  <dimension ref="A1:U17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A1" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1" s="21">
+        <v>2005</v>
+      </c>
+      <c r="D1" s="21">
+        <v>2006</v>
+      </c>
+      <c r="E1" s="21">
+        <v>2007</v>
+      </c>
+      <c r="F1" s="21">
+        <v>2008</v>
+      </c>
+      <c r="G1" s="21">
+        <v>2009</v>
+      </c>
+      <c r="H1" s="21">
+        <v>2010</v>
+      </c>
+      <c r="I1" s="21">
+        <v>2011</v>
+      </c>
+      <c r="J1" s="21">
+        <v>2012</v>
+      </c>
+      <c r="K1" s="21">
+        <v>2013</v>
+      </c>
+      <c r="L1" s="21">
+        <v>2014</v>
+      </c>
+      <c r="M1" s="21">
+        <v>2015</v>
+      </c>
+      <c r="N1" s="21">
+        <v>2016</v>
+      </c>
+      <c r="O1" s="21">
+        <v>2017</v>
+      </c>
+      <c r="P1" s="21">
+        <v>2018</v>
+      </c>
+      <c r="Q1" s="21">
+        <v>2019</v>
+      </c>
+      <c r="R1" s="21">
+        <v>2021</v>
+      </c>
+      <c r="S1" s="21">
+        <v>2022</v>
+      </c>
+      <c r="T1" s="21">
+        <v>2023</v>
+      </c>
+      <c r="U1" s="21">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A2" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" s="23">
+        <v>0.90900000000000003</v>
+      </c>
+      <c r="D2" s="23">
+        <v>0.90200000000000002</v>
+      </c>
+      <c r="E2" s="23">
+        <v>0.90200000000000002</v>
+      </c>
+      <c r="F2" s="23">
+        <v>0.89900000000000002</v>
+      </c>
+      <c r="G2" s="23">
+        <v>0.9</v>
+      </c>
+      <c r="H2" s="23">
+        <v>0.90200000000000002</v>
+      </c>
+      <c r="I2" s="23">
+        <v>0.9</v>
+      </c>
+      <c r="J2" s="23">
+        <v>0.89900000000000002</v>
+      </c>
+      <c r="K2" s="23">
+        <v>0.89700000000000002</v>
+      </c>
+      <c r="L2" s="23">
+        <v>0.89700000000000002</v>
+      </c>
+      <c r="M2" s="23">
+        <v>0.89700000000000002</v>
+      </c>
+      <c r="N2" s="23">
+        <v>0.89900000000000002</v>
+      </c>
+      <c r="O2" s="23">
+        <v>0.9</v>
+      </c>
+      <c r="P2" s="23">
+        <v>0.90100000000000002</v>
+      </c>
+      <c r="Q2" s="23">
+        <v>0.89900000000000002</v>
+      </c>
+      <c r="R2" s="23">
+        <v>0.92</v>
+      </c>
+      <c r="S2" s="23">
+        <v>0.91100000000000003</v>
+      </c>
+      <c r="T2" s="23">
+        <v>0.90700000000000003</v>
+      </c>
+      <c r="U2" s="24">
+        <v>0.90400000000000003</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="16">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="D3" s="16">
+        <v>0.05</v>
+      </c>
+      <c r="E3" s="16">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="F3" s="16">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="G3" s="16">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="H3" s="16">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="I3" s="16">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="J3" s="16">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="K3" s="16">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="L3" s="16">
+        <v>5.5E-2</v>
+      </c>
+      <c r="M3" s="16">
+        <v>5.5E-2</v>
+      </c>
+      <c r="N3" s="16">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="O3" s="16">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="P3" s="16">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="Q3" s="16">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="R3" s="16">
+        <v>0.03</v>
+      </c>
+      <c r="S3" s="16">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="T3" s="16">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="U3" s="25">
+        <v>4.2999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="16">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="D4" s="16">
+        <v>0.03</v>
+      </c>
+      <c r="E4" s="16">
+        <v>0.03</v>
+      </c>
+      <c r="F4" s="16">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="G4" s="16">
+        <v>0.03</v>
+      </c>
+      <c r="H4" s="16">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="I4" s="16">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="J4" s="16">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="K4" s="16">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="L4" s="16">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="M4" s="16">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="N4" s="16">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="O4" s="16">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="P4" s="16">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="Q4" s="16">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="R4" s="16">
+        <v>2.7E-2</v>
+      </c>
+      <c r="S4" s="16">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="T4" s="16">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="U4" s="25">
+        <v>2.8000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" s="28">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="D5" s="28">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="E5" s="28">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="F5" s="28">
+        <v>1.9E-2</v>
+      </c>
+      <c r="G5" s="28">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="H5" s="28">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="I5" s="28">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="J5" s="28">
+        <v>1.9E-2</v>
+      </c>
+      <c r="K5" s="28">
+        <v>0.02</v>
+      </c>
+      <c r="L5" s="28">
+        <v>1.9E-2</v>
+      </c>
+      <c r="M5" s="28">
+        <v>1.9E-2</v>
+      </c>
+      <c r="N5" s="28">
+        <v>1.9E-2</v>
+      </c>
+      <c r="O5" s="28">
+        <v>1.9E-2</v>
+      </c>
+      <c r="P5" s="28">
+        <v>0.02</v>
+      </c>
+      <c r="Q5" s="28">
+        <v>0.02</v>
+      </c>
+      <c r="R5" s="28">
+        <v>2.3E-2</v>
+      </c>
+      <c r="S5" s="28">
+        <v>2.4E-2</v>
+      </c>
+      <c r="T5" s="28">
+        <v>2.3E-2</v>
+      </c>
+      <c r="U5" s="29">
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A6" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="23">
+        <v>0.94899999999999995</v>
+      </c>
+      <c r="D6" s="23">
+        <v>0.94499999999999995</v>
+      </c>
+      <c r="E6" s="23">
+        <v>0.94499999999999995</v>
+      </c>
+      <c r="F6" s="23">
+        <v>0.94299999999999995</v>
+      </c>
+      <c r="G6" s="23">
+        <v>0.94499999999999995</v>
+      </c>
+      <c r="H6" s="23">
+        <v>0.94799999999999995</v>
+      </c>
+      <c r="I6" s="23">
+        <v>0.94799999999999995</v>
+      </c>
+      <c r="J6" s="23">
+        <v>0.94799999999999995</v>
+      </c>
+      <c r="K6" s="23">
+        <v>0.94799999999999995</v>
+      </c>
+      <c r="L6" s="23">
+        <v>0.94799999999999995</v>
+      </c>
+      <c r="M6" s="23">
+        <v>0.95099999999999996</v>
+      </c>
+      <c r="N6" s="23">
+        <v>0.95199999999999996</v>
+      </c>
+      <c r="O6" s="23">
+        <v>0.95299999999999996</v>
+      </c>
+      <c r="P6" s="23">
+        <v>0.95399999999999996</v>
+      </c>
+      <c r="Q6" s="23">
+        <v>0.95299999999999996</v>
+      </c>
+      <c r="R6" s="23">
+        <v>0.95399999999999996</v>
+      </c>
+      <c r="S6" s="23">
+        <v>0.95</v>
+      </c>
+      <c r="T6" s="23">
+        <v>0.95199999999999996</v>
+      </c>
+      <c r="U6" s="24">
+        <v>0.94799999999999995</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A7" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" s="16">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="D7" s="16">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="E7" s="16">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="F7" s="16">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="G7" s="16">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="H7" s="16">
+        <v>1.6E-2</v>
+      </c>
+      <c r="I7" s="16">
+        <v>1.6E-2</v>
+      </c>
+      <c r="J7" s="16">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="K7" s="16">
+        <v>1.6E-2</v>
+      </c>
+      <c r="L7" s="16">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="M7" s="16">
+        <v>1.6E-2</v>
+      </c>
+      <c r="N7" s="16">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O7" s="16">
+        <v>1.4E-2</v>
+      </c>
+      <c r="P7" s="16">
+        <v>1.4E-2</v>
+      </c>
+      <c r="Q7" s="16">
+        <v>1.4E-2</v>
+      </c>
+      <c r="R7" s="16">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="S7" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="T7" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="U7" s="25">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A8" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="16">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="D8" s="16">
+        <v>1.9E-2</v>
+      </c>
+      <c r="E8" s="16">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="F8" s="16">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="G8" s="16">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="H8" s="16">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="I8" s="16">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="J8" s="16">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="K8" s="16">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="L8" s="16">
+        <v>1.6E-2</v>
+      </c>
+      <c r="M8" s="16">
+        <v>1.6E-2</v>
+      </c>
+      <c r="N8" s="16">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="O8" s="16">
+        <v>1.6E-2</v>
+      </c>
+      <c r="P8" s="16">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="Q8" s="16">
+        <v>1.6E-2</v>
+      </c>
+      <c r="R8" s="16">
+        <v>1.6E-2</v>
+      </c>
+      <c r="S8" s="16">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="T8" s="16">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="U8" s="25">
+        <v>1.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A9" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="28">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="D9" s="28">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="E9" s="28">
+        <v>1.9E-2</v>
+      </c>
+      <c r="F9" s="28">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="G9" s="28">
+        <v>0.02</v>
+      </c>
+      <c r="H9" s="28">
+        <v>1.9E-2</v>
+      </c>
+      <c r="I9" s="28">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="J9" s="28">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="K9" s="28">
+        <v>1.9E-2</v>
+      </c>
+      <c r="L9" s="28">
+        <v>1.9E-2</v>
+      </c>
+      <c r="M9" s="28">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="N9" s="28">
+        <v>1.6E-2</v>
+      </c>
+      <c r="O9" s="28">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="P9" s="28">
+        <v>1.6E-2</v>
+      </c>
+      <c r="Q9" s="28">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="R9" s="28">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="S9" s="28">
+        <v>2.3E-2</v>
+      </c>
+      <c r="T9" s="28">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="U9" s="29">
+        <v>2.1999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A10" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" s="23">
+        <v>0.93200000000000005</v>
+      </c>
+      <c r="D10" s="23">
+        <v>0.93300000000000005</v>
+      </c>
+      <c r="E10" s="23">
+        <v>0.92800000000000005</v>
+      </c>
+      <c r="F10" s="23">
+        <v>0.91800000000000004</v>
+      </c>
+      <c r="G10" s="23">
+        <v>0.91900000000000004</v>
+      </c>
+      <c r="H10" s="23">
+        <v>0.92900000000000005</v>
+      </c>
+      <c r="I10" s="23">
+        <v>0.92500000000000004</v>
+      </c>
+      <c r="J10" s="23">
+        <v>0.93</v>
+      </c>
+      <c r="K10" s="23">
+        <v>0.93400000000000005</v>
+      </c>
+      <c r="L10" s="23">
+        <v>0.93100000000000005</v>
+      </c>
+      <c r="M10" s="23">
+        <v>0.93400000000000005</v>
+      </c>
+      <c r="N10" s="23">
+        <v>0.93600000000000005</v>
+      </c>
+      <c r="O10" s="23">
+        <v>0.94</v>
+      </c>
+      <c r="P10" s="23">
+        <v>0.93799999999999994</v>
+      </c>
+      <c r="Q10" s="23">
+        <v>0.93500000000000005</v>
+      </c>
+      <c r="R10" s="23">
+        <v>0.94199999999999995</v>
+      </c>
+      <c r="S10" s="23">
+        <v>0.93400000000000005</v>
+      </c>
+      <c r="T10" s="23">
+        <v>0.94099999999999995</v>
+      </c>
+      <c r="U10" s="24">
+        <v>0.92400000000000004</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A11" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" s="16">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="D11" s="16">
+        <v>2.4E-2</v>
+      </c>
+      <c r="E11" s="16">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="F11" s="16">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="G11" s="16">
+        <v>0.03</v>
+      </c>
+      <c r="H11" s="16">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I11" s="16">
+        <v>2.7E-2</v>
+      </c>
+      <c r="J11" s="16">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="K11" s="16">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="L11" s="16">
+        <v>2.7E-2</v>
+      </c>
+      <c r="M11" s="16">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="N11" s="16">
+        <v>2.4E-2</v>
+      </c>
+      <c r="O11" s="16">
+        <v>0.02</v>
+      </c>
+      <c r="P11" s="16">
+        <v>0.02</v>
+      </c>
+      <c r="Q11" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="R11" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="S11" s="16">
+        <v>1.6E-2</v>
+      </c>
+      <c r="T11" s="16">
+        <v>1.2E-2</v>
+      </c>
+      <c r="U11" s="25">
+        <v>1.9E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A12" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" s="16">
+        <v>1.6E-2</v>
+      </c>
+      <c r="D12" s="16">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="E12" s="16">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="F12" s="16">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="G12" s="16">
+        <v>1.9E-2</v>
+      </c>
+      <c r="H12" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="I12" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="J12" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="K12" s="16">
+        <v>1.9E-2</v>
+      </c>
+      <c r="L12" s="16">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="M12" s="16">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="N12" s="16">
+        <v>1.9E-2</v>
+      </c>
+      <c r="O12" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="P12" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="Q12" s="16">
+        <v>2.3E-2</v>
+      </c>
+      <c r="R12" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="S12" s="16">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="T12" s="16">
+        <v>2.3E-2</v>
+      </c>
+      <c r="U12" s="25">
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A13" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" s="16">
+        <v>2.3E-2</v>
+      </c>
+      <c r="D13" s="16">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="E13" s="16">
+        <v>2.3E-2</v>
+      </c>
+      <c r="F13" s="16">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="G13" s="16">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="H13" s="16">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="I13" s="16">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="J13" s="16">
+        <v>2.4E-2</v>
+      </c>
+      <c r="K13" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="L13" s="16">
+        <v>2.4E-2</v>
+      </c>
+      <c r="M13" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="N13" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="O13" s="16">
+        <v>1.9E-2</v>
+      </c>
+      <c r="P13" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="Q13" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="R13" s="16">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="S13" s="16">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="T13" s="16">
+        <v>2.4E-2</v>
+      </c>
+      <c r="U13" s="25">
+        <v>3.2000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A14" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" s="23">
+        <v>0.89800000000000002</v>
+      </c>
+      <c r="D14" s="23">
+        <v>0.90300000000000002</v>
+      </c>
+      <c r="E14" s="23">
+        <v>0.89400000000000002</v>
+      </c>
+      <c r="F14" s="23">
+        <v>0.86799999999999999</v>
+      </c>
+      <c r="G14" s="23">
+        <v>0.878</v>
+      </c>
+      <c r="H14" s="23">
+        <v>0.88300000000000001</v>
+      </c>
+      <c r="I14" s="23">
+        <v>0.88800000000000001</v>
+      </c>
+      <c r="J14" s="23">
+        <v>0.89400000000000002</v>
+      </c>
+      <c r="K14" s="23">
+        <v>0.9</v>
+      </c>
+      <c r="L14" s="23">
+        <v>0.89700000000000002</v>
+      </c>
+      <c r="M14" s="23">
+        <v>0.90200000000000002</v>
+      </c>
+      <c r="N14" s="23">
+        <v>0.90600000000000003</v>
+      </c>
+      <c r="O14" s="23">
+        <v>0.91200000000000003</v>
+      </c>
+      <c r="P14" s="23">
+        <v>0.91100000000000003</v>
+      </c>
+      <c r="Q14" s="23">
+        <v>0.90500000000000003</v>
+      </c>
+      <c r="R14" s="23">
+        <v>0.91600000000000004</v>
+      </c>
+      <c r="S14" s="23">
+        <v>0.91</v>
+      </c>
+      <c r="T14" s="23">
+        <v>0.91300000000000003</v>
+      </c>
+      <c r="U14" s="24">
+        <v>0.879</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A15" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="16">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="D15" s="16">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="E15" s="16">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="F15" s="16">
+        <v>0.06</v>
+      </c>
+      <c r="G15" s="16">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="H15" s="16">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="I15" s="16">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="J15" s="16">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="K15" s="16">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="L15" s="16">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="M15" s="16">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="N15" s="16">
+        <v>3.9E-2</v>
+      </c>
+      <c r="O15" s="16">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="P15" s="16">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="Q15" s="16">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="R15" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="S15" s="16">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="T15" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="U15" s="25">
+        <v>3.9E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A16" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" s="16">
+        <v>1.9E-2</v>
+      </c>
+      <c r="D16" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="E16" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="F16" s="16">
+        <v>0.02</v>
+      </c>
+      <c r="G16" s="16">
+        <v>2.4E-2</v>
+      </c>
+      <c r="H16" s="16">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="I16" s="16">
+        <v>0.03</v>
+      </c>
+      <c r="J16" s="16">
+        <v>0.03</v>
+      </c>
+      <c r="K16" s="16">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="L16" s="16">
+        <v>2.7E-2</v>
+      </c>
+      <c r="M16" s="16">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="N16" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="O16" s="16">
+        <v>2.7E-2</v>
+      </c>
+      <c r="P16" s="16">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Q16" s="16">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="R16" s="16">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="S16" s="16">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="T16" s="16">
+        <v>0.03</v>
+      </c>
+      <c r="U16" s="25">
+        <v>4.2999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A17" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" s="16">
+        <v>3.1E-2</v>
+      </c>
+      <c r="D17" s="16">
+        <v>0.03</v>
+      </c>
+      <c r="E17" s="16">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="F17" s="16">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="G17" s="16">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="H17" s="16">
+        <v>3.9E-2</v>
+      </c>
+      <c r="I17" s="16">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="J17" s="16">
+        <v>3.1E-2</v>
+      </c>
+      <c r="K17" s="16">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="L17" s="16">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="M17" s="16">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="N17" s="16">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="O17" s="16">
+        <v>2.4E-2</v>
+      </c>
+      <c r="P17" s="16">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="Q17" s="16">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="R17" s="16">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="S17" s="16">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="T17" s="16">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="U17" s="25">
+        <v>3.9E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E2DE309-0A33-432C-8E49-F742722252E1}">
+  <dimension ref="B2:B4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC4EA228-5174-414F-9D98-35BA988BDDB6}">
   <dimension ref="A1:AK5"/>
@@ -2057,6 +3198,174 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0F04B52-C20A-45EF-8E08-B582B76C4F3E}">
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="7">
+        <v>2014</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="30">
+        <v>3.1E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="7">
+        <v>2014</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="30">
+        <v>9.8000000000000004E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>2014</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="30">
+        <v>0.51100000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="7">
+        <v>2014</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="30">
+        <v>0.19500000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="7">
+        <v>2014</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="30">
+        <v>0.129</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="7">
+        <v>2014</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="30">
+        <v>3.1E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="30">
+        <v>3.5000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="30">
+        <v>8.5999999999999993E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="7">
+        <v>2024</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="30">
+        <v>0.50700000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="30">
+        <v>0.19500000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="30">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="7">
+        <v>2024</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="30">
+        <v>5.1999999999999998E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{654F738A-CCCF-4CA4-B4DE-AA41ADEB3AAD}">
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2195,7 +3504,143 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{099B39EB-0231-4325-BB50-8A0B9EF2A58F}">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="7">
+        <v>2014</v>
+      </c>
+      <c r="C2" s="15">
+        <v>78905</v>
+      </c>
+      <c r="D2" s="16">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="7">
+        <v>2014</v>
+      </c>
+      <c r="C3" s="15">
+        <v>155713</v>
+      </c>
+      <c r="D3" s="16">
+        <v>0.17699999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="7">
+        <v>2014</v>
+      </c>
+      <c r="C4" s="15">
+        <v>250666</v>
+      </c>
+      <c r="D4" s="16">
+        <v>0.28499999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="7">
+        <v>2014</v>
+      </c>
+      <c r="C5" s="15">
+        <v>392879</v>
+      </c>
+      <c r="D5" s="16">
+        <v>0.44700000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="7">
+        <v>2024</v>
+      </c>
+      <c r="C6" s="15">
+        <v>81233</v>
+      </c>
+      <c r="D6" s="16">
+        <v>6.6000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="15">
+        <v>178453</v>
+      </c>
+      <c r="D7" s="16">
+        <v>0.14499999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="15">
+        <v>274030</v>
+      </c>
+      <c r="D8" s="16">
+        <v>0.222</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="7">
+        <v>2024</v>
+      </c>
+      <c r="C9" s="15">
+        <v>698921</v>
+      </c>
+      <c r="D9" s="16">
+        <v>0.56699999999999995</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C560FB4D-BD58-45FD-9F59-DE48E37ABADF}">
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2334,7 +3779,146 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B3ABC10-3240-4B0E-8B6B-5331B1D8AE07}">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="7">
+        <v>2014</v>
+      </c>
+      <c r="C2" s="31">
+        <v>55819</v>
+      </c>
+      <c r="D2" s="32">
+        <v>5.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="7">
+        <v>2014</v>
+      </c>
+      <c r="C3" s="31">
+        <v>78283</v>
+      </c>
+      <c r="D3" s="32">
+        <v>7.3999999999999996E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="7">
+        <v>2014</v>
+      </c>
+      <c r="C4" s="31">
+        <v>590929</v>
+      </c>
+      <c r="D4" s="32">
+        <v>0.56200000000000006</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="7">
+        <v>2014</v>
+      </c>
+      <c r="C5" s="31">
+        <v>311284</v>
+      </c>
+      <c r="D5" s="32">
+        <v>0.29599999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="7">
+        <v>2024</v>
+      </c>
+      <c r="C6" s="31">
+        <v>137675</v>
+      </c>
+      <c r="D6" s="32">
+        <v>9.1999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="31">
+        <v>110035</v>
+      </c>
+      <c r="D7" s="32">
+        <v>7.3999999999999996E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="31">
+        <v>711247</v>
+      </c>
+      <c r="D8" s="32">
+        <v>0.47699999999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="7">
+        <v>2024</v>
+      </c>
+      <c r="C9" s="31">
+        <v>473644</v>
+      </c>
+      <c r="D9" s="32">
+        <v>0.318</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECBFFC3B-7BC6-451A-8664-95E5A6D1CBC5}">
   <dimension ref="A1:C61"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3016,1139 +4600,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53D66845-253C-4802-AFB8-DEDA69A5A8E7}">
-  <dimension ref="A1:U17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="B1" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C1" s="21">
-        <v>2005</v>
-      </c>
-      <c r="D1" s="21">
-        <v>2006</v>
-      </c>
-      <c r="E1" s="21">
-        <v>2007</v>
-      </c>
-      <c r="F1" s="21">
-        <v>2008</v>
-      </c>
-      <c r="G1" s="21">
-        <v>2009</v>
-      </c>
-      <c r="H1" s="21">
-        <v>2010</v>
-      </c>
-      <c r="I1" s="21">
-        <v>2011</v>
-      </c>
-      <c r="J1" s="21">
-        <v>2012</v>
-      </c>
-      <c r="K1" s="21">
-        <v>2013</v>
-      </c>
-      <c r="L1" s="21">
-        <v>2014</v>
-      </c>
-      <c r="M1" s="21">
-        <v>2015</v>
-      </c>
-      <c r="N1" s="21">
-        <v>2016</v>
-      </c>
-      <c r="O1" s="21">
-        <v>2017</v>
-      </c>
-      <c r="P1" s="21">
-        <v>2018</v>
-      </c>
-      <c r="Q1" s="21">
-        <v>2019</v>
-      </c>
-      <c r="R1" s="21">
-        <v>2021</v>
-      </c>
-      <c r="S1" s="21">
-        <v>2022</v>
-      </c>
-      <c r="T1" s="21">
-        <v>2023</v>
-      </c>
-      <c r="U1" s="21">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A2" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="B2" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="C2" s="23">
-        <v>0.90900000000000003</v>
-      </c>
-      <c r="D2" s="23">
-        <v>0.90200000000000002</v>
-      </c>
-      <c r="E2" s="23">
-        <v>0.90200000000000002</v>
-      </c>
-      <c r="F2" s="23">
-        <v>0.89900000000000002</v>
-      </c>
-      <c r="G2" s="23">
-        <v>0.9</v>
-      </c>
-      <c r="H2" s="23">
-        <v>0.90200000000000002</v>
-      </c>
-      <c r="I2" s="23">
-        <v>0.9</v>
-      </c>
-      <c r="J2" s="23">
-        <v>0.89900000000000002</v>
-      </c>
-      <c r="K2" s="23">
-        <v>0.89700000000000002</v>
-      </c>
-      <c r="L2" s="23">
-        <v>0.89700000000000002</v>
-      </c>
-      <c r="M2" s="23">
-        <v>0.89700000000000002</v>
-      </c>
-      <c r="N2" s="23">
-        <v>0.89900000000000002</v>
-      </c>
-      <c r="O2" s="23">
-        <v>0.9</v>
-      </c>
-      <c r="P2" s="23">
-        <v>0.90100000000000002</v>
-      </c>
-      <c r="Q2" s="23">
-        <v>0.89900000000000002</v>
-      </c>
-      <c r="R2" s="23">
-        <v>0.92</v>
-      </c>
-      <c r="S2" s="23">
-        <v>0.91100000000000003</v>
-      </c>
-      <c r="T2" s="23">
-        <v>0.90700000000000003</v>
-      </c>
-      <c r="U2" s="24">
-        <v>0.90400000000000003</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A3" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="C3" s="16">
-        <v>4.8000000000000001E-2</v>
-      </c>
-      <c r="D3" s="16">
-        <v>0.05</v>
-      </c>
-      <c r="E3" s="16">
-        <v>5.0999999999999997E-2</v>
-      </c>
-      <c r="F3" s="16">
-        <v>5.1999999999999998E-2</v>
-      </c>
-      <c r="G3" s="16">
-        <v>5.1999999999999998E-2</v>
-      </c>
-      <c r="H3" s="16">
-        <v>5.1999999999999998E-2</v>
-      </c>
-      <c r="I3" s="16">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="J3" s="16">
-        <v>5.1999999999999998E-2</v>
-      </c>
-      <c r="K3" s="16">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="L3" s="16">
-        <v>5.5E-2</v>
-      </c>
-      <c r="M3" s="16">
-        <v>5.5E-2</v>
-      </c>
-      <c r="N3" s="16">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="O3" s="16">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="P3" s="16">
-        <v>5.1999999999999998E-2</v>
-      </c>
-      <c r="Q3" s="16">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="R3" s="16">
-        <v>0.03</v>
-      </c>
-      <c r="S3" s="16">
-        <v>3.6999999999999998E-2</v>
-      </c>
-      <c r="T3" s="16">
-        <v>4.1000000000000002E-2</v>
-      </c>
-      <c r="U3" s="25">
-        <v>4.2999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A4" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="C4" s="16">
-        <v>2.5999999999999999E-2</v>
-      </c>
-      <c r="D4" s="16">
-        <v>0.03</v>
-      </c>
-      <c r="E4" s="16">
-        <v>0.03</v>
-      </c>
-      <c r="F4" s="16">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="G4" s="16">
-        <v>0.03</v>
-      </c>
-      <c r="H4" s="16">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="I4" s="16">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="J4" s="16">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="K4" s="16">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="L4" s="16">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="M4" s="16">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="N4" s="16">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="O4" s="16">
-        <v>2.8000000000000001E-2</v>
-      </c>
-      <c r="P4" s="16">
-        <v>2.8000000000000001E-2</v>
-      </c>
-      <c r="Q4" s="16">
-        <v>2.8000000000000001E-2</v>
-      </c>
-      <c r="R4" s="16">
-        <v>2.7E-2</v>
-      </c>
-      <c r="S4" s="16">
-        <v>2.8000000000000001E-2</v>
-      </c>
-      <c r="T4" s="16">
-        <v>2.8000000000000001E-2</v>
-      </c>
-      <c r="U4" s="25">
-        <v>2.8000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A5" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="B5" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="C5" s="28">
-        <v>1.7000000000000001E-2</v>
-      </c>
-      <c r="D5" s="28">
-        <v>1.7000000000000001E-2</v>
-      </c>
-      <c r="E5" s="28">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="F5" s="28">
-        <v>1.9E-2</v>
-      </c>
-      <c r="G5" s="28">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="H5" s="28">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="I5" s="28">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="J5" s="28">
-        <v>1.9E-2</v>
-      </c>
-      <c r="K5" s="28">
-        <v>0.02</v>
-      </c>
-      <c r="L5" s="28">
-        <v>1.9E-2</v>
-      </c>
-      <c r="M5" s="28">
-        <v>1.9E-2</v>
-      </c>
-      <c r="N5" s="28">
-        <v>1.9E-2</v>
-      </c>
-      <c r="O5" s="28">
-        <v>1.9E-2</v>
-      </c>
-      <c r="P5" s="28">
-        <v>0.02</v>
-      </c>
-      <c r="Q5" s="28">
-        <v>0.02</v>
-      </c>
-      <c r="R5" s="28">
-        <v>2.3E-2</v>
-      </c>
-      <c r="S5" s="28">
-        <v>2.4E-2</v>
-      </c>
-      <c r="T5" s="28">
-        <v>2.3E-2</v>
-      </c>
-      <c r="U5" s="29">
-        <v>2.5000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A6" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="23">
-        <v>0.94899999999999995</v>
-      </c>
-      <c r="D6" s="23">
-        <v>0.94499999999999995</v>
-      </c>
-      <c r="E6" s="23">
-        <v>0.94499999999999995</v>
-      </c>
-      <c r="F6" s="23">
-        <v>0.94299999999999995</v>
-      </c>
-      <c r="G6" s="23">
-        <v>0.94499999999999995</v>
-      </c>
-      <c r="H6" s="23">
-        <v>0.94799999999999995</v>
-      </c>
-      <c r="I6" s="23">
-        <v>0.94799999999999995</v>
-      </c>
-      <c r="J6" s="23">
-        <v>0.94799999999999995</v>
-      </c>
-      <c r="K6" s="23">
-        <v>0.94799999999999995</v>
-      </c>
-      <c r="L6" s="23">
-        <v>0.94799999999999995</v>
-      </c>
-      <c r="M6" s="23">
-        <v>0.95099999999999996</v>
-      </c>
-      <c r="N6" s="23">
-        <v>0.95199999999999996</v>
-      </c>
-      <c r="O6" s="23">
-        <v>0.95299999999999996</v>
-      </c>
-      <c r="P6" s="23">
-        <v>0.95399999999999996</v>
-      </c>
-      <c r="Q6" s="23">
-        <v>0.95299999999999996</v>
-      </c>
-      <c r="R6" s="23">
-        <v>0.95399999999999996</v>
-      </c>
-      <c r="S6" s="23">
-        <v>0.95</v>
-      </c>
-      <c r="T6" s="23">
-        <v>0.95199999999999996</v>
-      </c>
-      <c r="U6" s="24">
-        <v>0.94799999999999995</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A7" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="C7" s="16">
-        <v>1.7000000000000001E-2</v>
-      </c>
-      <c r="D7" s="16">
-        <v>1.7000000000000001E-2</v>
-      </c>
-      <c r="E7" s="16">
-        <v>1.7000000000000001E-2</v>
-      </c>
-      <c r="F7" s="16">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="G7" s="16">
-        <v>1.7000000000000001E-2</v>
-      </c>
-      <c r="H7" s="16">
-        <v>1.6E-2</v>
-      </c>
-      <c r="I7" s="16">
-        <v>1.6E-2</v>
-      </c>
-      <c r="J7" s="16">
-        <v>1.7000000000000001E-2</v>
-      </c>
-      <c r="K7" s="16">
-        <v>1.6E-2</v>
-      </c>
-      <c r="L7" s="16">
-        <v>1.7000000000000001E-2</v>
-      </c>
-      <c r="M7" s="16">
-        <v>1.6E-2</v>
-      </c>
-      <c r="N7" s="16">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="O7" s="16">
-        <v>1.4E-2</v>
-      </c>
-      <c r="P7" s="16">
-        <v>1.4E-2</v>
-      </c>
-      <c r="Q7" s="16">
-        <v>1.4E-2</v>
-      </c>
-      <c r="R7" s="16">
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="S7" s="16">
-        <v>0.01</v>
-      </c>
-      <c r="T7" s="16">
-        <v>0.01</v>
-      </c>
-      <c r="U7" s="25">
-        <v>1.0999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A8" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" s="16">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="D8" s="16">
-        <v>1.9E-2</v>
-      </c>
-      <c r="E8" s="16">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="F8" s="16">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="G8" s="16">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="H8" s="16">
-        <v>1.7000000000000001E-2</v>
-      </c>
-      <c r="I8" s="16">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="J8" s="16">
-        <v>1.7000000000000001E-2</v>
-      </c>
-      <c r="K8" s="16">
-        <v>1.7000000000000001E-2</v>
-      </c>
-      <c r="L8" s="16">
-        <v>1.6E-2</v>
-      </c>
-      <c r="M8" s="16">
-        <v>1.6E-2</v>
-      </c>
-      <c r="N8" s="16">
-        <v>1.7000000000000001E-2</v>
-      </c>
-      <c r="O8" s="16">
-        <v>1.6E-2</v>
-      </c>
-      <c r="P8" s="16">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="Q8" s="16">
-        <v>1.6E-2</v>
-      </c>
-      <c r="R8" s="16">
-        <v>1.6E-2</v>
-      </c>
-      <c r="S8" s="16">
-        <v>1.7000000000000001E-2</v>
-      </c>
-      <c r="T8" s="16">
-        <v>1.7000000000000001E-2</v>
-      </c>
-      <c r="U8" s="25">
-        <v>1.7999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A9" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="B9" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="C9" s="28">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="D9" s="28">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="E9" s="28">
-        <v>1.9E-2</v>
-      </c>
-      <c r="F9" s="28">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="G9" s="28">
-        <v>0.02</v>
-      </c>
-      <c r="H9" s="28">
-        <v>1.9E-2</v>
-      </c>
-      <c r="I9" s="28">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="J9" s="28">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="K9" s="28">
-        <v>1.9E-2</v>
-      </c>
-      <c r="L9" s="28">
-        <v>1.9E-2</v>
-      </c>
-      <c r="M9" s="28">
-        <v>1.7000000000000001E-2</v>
-      </c>
-      <c r="N9" s="28">
-        <v>1.6E-2</v>
-      </c>
-      <c r="O9" s="28">
-        <v>1.7000000000000001E-2</v>
-      </c>
-      <c r="P9" s="28">
-        <v>1.6E-2</v>
-      </c>
-      <c r="Q9" s="28">
-        <v>1.7000000000000001E-2</v>
-      </c>
-      <c r="R9" s="28">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="S9" s="28">
-        <v>2.3E-2</v>
-      </c>
-      <c r="T9" s="28">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="U9" s="29">
-        <v>2.1999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A10" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="B10" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" s="23">
-        <v>0.93200000000000005</v>
-      </c>
-      <c r="D10" s="23">
-        <v>0.93300000000000005</v>
-      </c>
-      <c r="E10" s="23">
-        <v>0.92800000000000005</v>
-      </c>
-      <c r="F10" s="23">
-        <v>0.91800000000000004</v>
-      </c>
-      <c r="G10" s="23">
-        <v>0.91900000000000004</v>
-      </c>
-      <c r="H10" s="23">
-        <v>0.92900000000000005</v>
-      </c>
-      <c r="I10" s="23">
-        <v>0.92500000000000004</v>
-      </c>
-      <c r="J10" s="23">
-        <v>0.93</v>
-      </c>
-      <c r="K10" s="23">
-        <v>0.93400000000000005</v>
-      </c>
-      <c r="L10" s="23">
-        <v>0.93100000000000005</v>
-      </c>
-      <c r="M10" s="23">
-        <v>0.93400000000000005</v>
-      </c>
-      <c r="N10" s="23">
-        <v>0.93600000000000005</v>
-      </c>
-      <c r="O10" s="23">
-        <v>0.94</v>
-      </c>
-      <c r="P10" s="23">
-        <v>0.93799999999999994</v>
-      </c>
-      <c r="Q10" s="23">
-        <v>0.93500000000000005</v>
-      </c>
-      <c r="R10" s="23">
-        <v>0.94199999999999995</v>
-      </c>
-      <c r="S10" s="23">
-        <v>0.93400000000000005</v>
-      </c>
-      <c r="T10" s="23">
-        <v>0.94099999999999995</v>
-      </c>
-      <c r="U10" s="24">
-        <v>0.92400000000000004</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A11" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" s="16">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="D11" s="16">
-        <v>2.4E-2</v>
-      </c>
-      <c r="E11" s="16">
-        <v>3.2000000000000001E-2</v>
-      </c>
-      <c r="F11" s="16">
-        <v>3.2000000000000001E-2</v>
-      </c>
-      <c r="G11" s="16">
-        <v>0.03</v>
-      </c>
-      <c r="H11" s="16">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="I11" s="16">
-        <v>2.7E-2</v>
-      </c>
-      <c r="J11" s="16">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="K11" s="16">
-        <v>2.5999999999999999E-2</v>
-      </c>
-      <c r="L11" s="16">
-        <v>2.7E-2</v>
-      </c>
-      <c r="M11" s="16">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="N11" s="16">
-        <v>2.4E-2</v>
-      </c>
-      <c r="O11" s="16">
-        <v>0.02</v>
-      </c>
-      <c r="P11" s="16">
-        <v>0.02</v>
-      </c>
-      <c r="Q11" s="16">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="R11" s="16">
-        <v>0.01</v>
-      </c>
-      <c r="S11" s="16">
-        <v>1.6E-2</v>
-      </c>
-      <c r="T11" s="16">
-        <v>1.2E-2</v>
-      </c>
-      <c r="U11" s="25">
-        <v>1.9E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A12" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" s="16">
-        <v>1.6E-2</v>
-      </c>
-      <c r="D12" s="16">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="E12" s="16">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="F12" s="16">
-        <v>1.7000000000000001E-2</v>
-      </c>
-      <c r="G12" s="16">
-        <v>1.9E-2</v>
-      </c>
-      <c r="H12" s="16">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="I12" s="16">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="J12" s="16">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="K12" s="16">
-        <v>1.9E-2</v>
-      </c>
-      <c r="L12" s="16">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="M12" s="16">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="N12" s="16">
-        <v>1.9E-2</v>
-      </c>
-      <c r="O12" s="16">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="P12" s="16">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="Q12" s="16">
-        <v>2.3E-2</v>
-      </c>
-      <c r="R12" s="16">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="S12" s="16">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="T12" s="16">
-        <v>2.3E-2</v>
-      </c>
-      <c r="U12" s="25">
-        <v>2.5000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A13" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="C13" s="16">
-        <v>2.3E-2</v>
-      </c>
-      <c r="D13" s="16">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="E13" s="16">
-        <v>2.3E-2</v>
-      </c>
-      <c r="F13" s="16">
-        <v>3.3000000000000002E-2</v>
-      </c>
-      <c r="G13" s="16">
-        <v>3.3000000000000002E-2</v>
-      </c>
-      <c r="H13" s="16">
-        <v>2.5999999999999999E-2</v>
-      </c>
-      <c r="I13" s="16">
-        <v>2.8000000000000001E-2</v>
-      </c>
-      <c r="J13" s="16">
-        <v>2.4E-2</v>
-      </c>
-      <c r="K13" s="16">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="L13" s="16">
-        <v>2.4E-2</v>
-      </c>
-      <c r="M13" s="16">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="N13" s="16">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="O13" s="16">
-        <v>1.9E-2</v>
-      </c>
-      <c r="P13" s="16">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="Q13" s="16">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="R13" s="16">
-        <v>2.5999999999999999E-2</v>
-      </c>
-      <c r="S13" s="16">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="T13" s="16">
-        <v>2.4E-2</v>
-      </c>
-      <c r="U13" s="25">
-        <v>3.2000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A14" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="B14" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="C14" s="23">
-        <v>0.89800000000000002</v>
-      </c>
-      <c r="D14" s="23">
-        <v>0.90300000000000002</v>
-      </c>
-      <c r="E14" s="23">
-        <v>0.89400000000000002</v>
-      </c>
-      <c r="F14" s="23">
-        <v>0.86799999999999999</v>
-      </c>
-      <c r="G14" s="23">
-        <v>0.878</v>
-      </c>
-      <c r="H14" s="23">
-        <v>0.88300000000000001</v>
-      </c>
-      <c r="I14" s="23">
-        <v>0.88800000000000001</v>
-      </c>
-      <c r="J14" s="23">
-        <v>0.89400000000000002</v>
-      </c>
-      <c r="K14" s="23">
-        <v>0.9</v>
-      </c>
-      <c r="L14" s="23">
-        <v>0.89700000000000002</v>
-      </c>
-      <c r="M14" s="23">
-        <v>0.90200000000000002</v>
-      </c>
-      <c r="N14" s="23">
-        <v>0.90600000000000003</v>
-      </c>
-      <c r="O14" s="23">
-        <v>0.91200000000000003</v>
-      </c>
-      <c r="P14" s="23">
-        <v>0.91100000000000003</v>
-      </c>
-      <c r="Q14" s="23">
-        <v>0.90500000000000003</v>
-      </c>
-      <c r="R14" s="23">
-        <v>0.91600000000000004</v>
-      </c>
-      <c r="S14" s="23">
-        <v>0.91</v>
-      </c>
-      <c r="T14" s="23">
-        <v>0.91300000000000003</v>
-      </c>
-      <c r="U14" s="24">
-        <v>0.879</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A15" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" s="16">
-        <v>5.1999999999999998E-2</v>
-      </c>
-      <c r="D15" s="16">
-        <v>4.3999999999999997E-2</v>
-      </c>
-      <c r="E15" s="16">
-        <v>5.1999999999999998E-2</v>
-      </c>
-      <c r="F15" s="16">
-        <v>0.06</v>
-      </c>
-      <c r="G15" s="16">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="H15" s="16">
-        <v>4.5999999999999999E-2</v>
-      </c>
-      <c r="I15" s="16">
-        <v>4.3999999999999997E-2</v>
-      </c>
-      <c r="J15" s="16">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="K15" s="16">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="L15" s="16">
-        <v>4.5999999999999999E-2</v>
-      </c>
-      <c r="M15" s="16">
-        <v>4.2999999999999997E-2</v>
-      </c>
-      <c r="N15" s="16">
-        <v>3.9E-2</v>
-      </c>
-      <c r="O15" s="16">
-        <v>3.6999999999999998E-2</v>
-      </c>
-      <c r="P15" s="16">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="Q15" s="16">
-        <v>3.6999999999999998E-2</v>
-      </c>
-      <c r="R15" s="16">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="S15" s="16">
-        <v>3.2000000000000001E-2</v>
-      </c>
-      <c r="T15" s="16">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="U15" s="25">
-        <v>3.9E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A16" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" s="16">
-        <v>1.9E-2</v>
-      </c>
-      <c r="D16" s="16">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="E16" s="16">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="F16" s="16">
-        <v>0.02</v>
-      </c>
-      <c r="G16" s="16">
-        <v>2.4E-2</v>
-      </c>
-      <c r="H16" s="16">
-        <v>3.2000000000000001E-2</v>
-      </c>
-      <c r="I16" s="16">
-        <v>0.03</v>
-      </c>
-      <c r="J16" s="16">
-        <v>0.03</v>
-      </c>
-      <c r="K16" s="16">
-        <v>2.5999999999999999E-2</v>
-      </c>
-      <c r="L16" s="16">
-        <v>2.7E-2</v>
-      </c>
-      <c r="M16" s="16">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="N16" s="16">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="O16" s="16">
-        <v>2.7E-2</v>
-      </c>
-      <c r="P16" s="16">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="Q16" s="16">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="R16" s="16">
-        <v>2.8000000000000001E-2</v>
-      </c>
-      <c r="S16" s="16">
-        <v>3.3000000000000002E-2</v>
-      </c>
-      <c r="T16" s="16">
-        <v>0.03</v>
-      </c>
-      <c r="U16" s="25">
-        <v>4.2999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A17" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="B17" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" s="16">
-        <v>3.1E-2</v>
-      </c>
-      <c r="D17" s="16">
-        <v>0.03</v>
-      </c>
-      <c r="E17" s="16">
-        <v>3.4000000000000002E-2</v>
-      </c>
-      <c r="F17" s="16">
-        <v>5.1999999999999998E-2</v>
-      </c>
-      <c r="G17" s="16">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="H17" s="16">
-        <v>3.9E-2</v>
-      </c>
-      <c r="I17" s="16">
-        <v>3.6999999999999998E-2</v>
-      </c>
-      <c r="J17" s="16">
-        <v>3.1E-2</v>
-      </c>
-      <c r="K17" s="16">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="L17" s="16">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="M17" s="16">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="N17" s="16">
-        <v>3.3000000000000002E-2</v>
-      </c>
-      <c r="O17" s="16">
-        <v>2.4E-2</v>
-      </c>
-      <c r="P17" s="16">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="Q17" s="16">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="R17" s="16">
-        <v>3.4000000000000002E-2</v>
-      </c>
-      <c r="S17" s="16">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="T17" s="16">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="U17" s="25">
-        <v>3.9E-2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E2DE309-0A33-432C-8E49-F742722252E1}">
-  <dimension ref="B2:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>